--- a/Data/Game_Results.xlsx
+++ b/Data/Game_Results.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,70 +531,70 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2026-08-11 22:07:52.788656</t>
+          <t xml:space="preserve"> 2026-08-11 22:08:16.921228</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.700332403182983</v>
+        <v>12.78197836875916</v>
       </c>
       <c r="C5" t="n">
-        <v>31</v>
+        <v>340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>&lt; 10 seconds</t>
+          <t>10–29 seconds</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>&lt; 100 points</t>
+          <t>100-499 points</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>18.23172924421643</v>
+        <v>26.59995113362146</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2026-08-11 22:08:16.921228</t>
+          <t xml:space="preserve"> 2026-08-11 22:09:49.791919</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.78197836875916</v>
+        <v>0.9957668781280518</v>
       </c>
       <c r="C6" t="n">
-        <v>340</v>
+        <v>17</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10–29 seconds</t>
+          <t>&lt; 10 seconds</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>100-499 points</t>
+          <t>&lt; 100 points</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>26.59995113362146</v>
+        <v>17.07226899528774</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2026-08-11 22:09:49.791919</t>
+          <t xml:space="preserve"> 2026-08-11 22:10:49.555555</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9957668781280518</v>
+        <v>10.99576687812805</v>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>&lt; 10 seconds</t>
+          <t>10–29 seconds</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -603,136 +603,110 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>17.07226899528774</v>
+        <v>4.91098079820269</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2026-08-11 22:10:49.555555</t>
+          <t xml:space="preserve"> 2026-08-11 22:11:46.388839</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.99576687812805</v>
+        <v>107.1608285903931</v>
       </c>
       <c r="C8" t="n">
-        <v>54</v>
+        <v>12791</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10–29 seconds</t>
+          <t>90+ seconds</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>&lt; 100 points</t>
+          <t>10000-49999 points</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.91098079820269</v>
+        <v>119.3626455511255</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2026-08-11 22:11:46.388839</t>
+          <t xml:space="preserve"> 2026-08-11 22:18:21.849750</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>107.1608285903931</v>
+        <v>0.7529363632202148</v>
       </c>
       <c r="C9" t="n">
-        <v>12791</v>
+        <v>13</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>90+ seconds</t>
+          <t>&lt; 10 seconds</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10000-49999 points</t>
+          <t>&lt; 100 points</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>119.3626455511255</v>
+        <v>17.26573537290804</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2026-08-11 22:18:21.849750</t>
+          <t xml:space="preserve"> 2026-08-11 22:47:28.879336</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7529363632202148</v>
+        <v>32.12995481491089</v>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>1404</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>&lt; 10 seconds</t>
+          <t>30–59 seconds</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>&lt; 100 points</t>
+          <t>1000-4999 points</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>17.26573537290804</v>
+        <v>43.69754044435913</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2026-08-11 22:47:28.879336</t>
+          <t xml:space="preserve"> 2026-08-18 15:39:37.275915</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32.12995481491089</v>
+        <v>4.388702869415283</v>
       </c>
       <c r="C11" t="n">
-        <v>1404</v>
+        <v>83</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>30–59 seconds</t>
+          <t>&lt; 10 seconds</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1000-4999 points</t>
+          <t>&lt; 100 points</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>43.69754044435913</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 2026-08-18 15:39:37.275915</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>4.388702869415283</v>
-      </c>
-      <c r="C12" t="n">
-        <v>83</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>&lt; 10 seconds</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>&lt; 100 points</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
         <v>18.91219398297025</v>
       </c>
     </row>
@@ -1131,7 +1105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1192,6 +1166,526 @@
         <v>16.5937196312774</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2026-08-20 15:49:02.085876</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.6629014015197754</v>
+      </c>
+      <c r="C3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>&lt; 10 seconds</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>&lt; 100 points</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>16.5937196312774</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-20 19:04:30.613762</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.1165409088134765</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>&lt; 10 seconds</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>&lt; 100 points</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>8.580677893978827</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-20 19:07:07.897435</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.5525596141815186</v>
+      </c>
+      <c r="C5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>&lt; 10 seconds</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>&lt; 100 points</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>16.28783531950899</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-20 19:34:07.238980</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.0059964656829833</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>&lt; 10 seconds</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>&lt; 100 points</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-20 19:35:20.432343</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.219968557357788</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>&lt; 10 seconds</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>&lt; 100 points</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>13.63831283904988</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-20 19:38:26.656771</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>6.137717008590698</v>
+      </c>
+      <c r="C8" t="n">
+        <v>123</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>&lt; 10 seconds</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>100-499 points</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>20.04002462606898</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-20 19:38:47.996052</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.6650376319885254</v>
+      </c>
+      <c r="C9" t="n">
+        <v>11</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>&lt; 10 seconds</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>&lt; 100 points</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>16.54041737023055</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-20 19:39:35.510349</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.932753801345825</v>
+      </c>
+      <c r="C10" t="n">
+        <v>35</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>&lt; 10 seconds</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>&lt; 100 points</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>18.10887655511459</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-20 19:41:38.512194</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>68.57633233070374</v>
+      </c>
+      <c r="C11" t="n">
+        <v>6836</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>60-89 seconds</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>5000-9999 points</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>99.68453791074668</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-20 19:45:46.696170</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>11.70449042320252</v>
+      </c>
+      <c r="C12" t="n">
+        <v>297</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>10–29 seconds</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>100-499 points</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>25.3748765867875</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-20 19:47:47.865085</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>40.54903721809387</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2400</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>30–59 seconds</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1000-4999 points</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>59.18759518485108</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-20 19:50:13.689818</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>31.57385468482971</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1771</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>30–59 seconds</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1000-4999 points</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>56.09071232125839</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-20 19:51:53.202755</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.0118162631988525</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>&lt; 10 seconds</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>&lt; 100 points</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-20 19:52:06.381507</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.3347604274749756</v>
+      </c>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>&lt; 10 seconds</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>&lt; 100 points</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>14.9360545322334</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-20 19:53:15.689284</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>54.74263262748718</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4164</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>30–59 seconds</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1000-4999 points</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>76.06503012624911</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-20 19:56:28.691857</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.5496106147766113</v>
+      </c>
+      <c r="C18" t="n">
+        <v>9</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>&lt; 10 seconds</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>&lt; 100 points</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>16.37522958623723</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-20 19:57:41.418609</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>62.76914858818054</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4839</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>60-89 seconds</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1000-4999 points</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>77.09201269795757</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-20 19:58:06.768919</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>14.07721257209778</v>
+      </c>
+      <c r="C20" t="n">
+        <v>386</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>10–29 seconds</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>100-499 points</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>27.4202011245525</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-20 19:58:50.274679</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>31.09034562110901</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1765</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>30–59 seconds</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1000-4999 points</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>56.7700347081906</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-20 20:01:49.515100</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>76.59435606002808</v>
+      </c>
+      <c r="C22" t="n">
+        <v>7902</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>60-89 seconds</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>5000-9999 points</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>103.1668703345073</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
